--- a/domain/tasks/20260310_115400_vd_ingame_masterdata_generation/specs/限界チャレンジ(VD)_アウトゲーム関連_ブロック基礎設計テンプレート.xlsx
+++ b/domain/tasks/20260310_115400_vd_ingame_masterdata_generation/specs/限界チャレンジ(VD)_アウトゲーム関連_ブロック基礎設計テンプレート.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junki.mizutani/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junki.mizutani/Documents/workspace/glow/glow-brain-repos/glow-brain-shuna/domain/tasks/20260310_115400_vd_ingame_masterdata_generation/specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{53AB9859-11C5-7147-A740-62F6A9244AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9091E9-3514-FA4E-86AA-05D4DF12E9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="920" yWindow="660" windowWidth="29320" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,6 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -64,9 +63,6 @@
     <t>■基本情報</t>
   </si>
   <si>
-    <t>⇩ボスブロックのみに記載するやつ</t>
-  </si>
-  <si>
     <t>インゲームID</t>
   </si>
   <si>
@@ -82,21 +78,9 @@
     <t>グループ切り替え</t>
   </si>
   <si>
-    <t>シーケンス行数目安</t>
-  </si>
-  <si>
     <t>リリースキー</t>
   </si>
   <si>
-    <t>dungeon_chi_normal_00001</t>
-  </si>
-  <si>
-    <t>ノーマルブロック（dungeon_normal）</t>
-  </si>
-  <si>
-    <t>3行（dungeon通常ブロック固定値）</t>
-  </si>
-  <si>
     <t>なし（デフォルトグループのみ）</t>
   </si>
   <si>
@@ -214,9 +198,6 @@
     <t>後半の主力・高火力アタッカー</t>
   </si>
   <si>
-    <t>■シーケンス構成（目安）</t>
-  </si>
-  <si>
     <t>行番号</t>
   </si>
   <si>
@@ -266,13 +247,80 @@
   </si>
   <si>
     <t>「チェンソーマンの世界に登場するゾンビたちが迫り来る！序盤は無属性のゾンビが波状攻撃をしかけてくるが、後半には黄属性の高火力ゾンビが押し寄せてくるぞ。緑属性のキャラで属性有利を取りながら突破しよう！」</t>
+  </si>
+  <si>
+    <t>シーケンス行数</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>行</t>
+    </r>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>⇩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ボスブロックのみに記載する</t>
+    </r>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>vd_chi_normal_00001</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>シーケンス構成</t>
+    </r>
+    <phoneticPr fontId="13"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -365,6 +413,35 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="MS Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="MS Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="MS Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -456,7 +533,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -511,16 +588,19 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -831,17 +911,17 @@
     </row>
     <row r="4" spans="1:13" ht="186" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="6"/>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="22"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
@@ -876,14 +956,14 @@
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
     </row>
-    <row r="7" spans="1:13" ht="24" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A7" s="2"/>
       <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>71</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -898,25 +978,25 @@
     <row r="8" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
       <c r="B8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -927,22 +1007,22 @@
     <row r="9" spans="1:13" ht="24" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="9" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="D9" s="9">
         <v>100</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="2"/>
@@ -954,7 +1034,7 @@
     <row r="10" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A10" s="2"/>
       <c r="B10" s="10" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -986,7 +1066,7 @@
     <row r="12" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A12" s="2"/>
       <c r="B12" s="7" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -1003,19 +1083,19 @@
     <row r="13" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A13" s="2"/>
       <c r="B13" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -1028,19 +1108,19 @@
     <row r="14" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A14" s="2"/>
       <c r="B14" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -1053,19 +1133,19 @@
     <row r="15" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A15" s="2"/>
       <c r="B15" s="11" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>33</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -1078,16 +1158,16 @@
     <row r="16" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A16" s="2"/>
       <c r="B16" s="11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F16" s="11">
         <v>1</v>
@@ -1118,13 +1198,13 @@
     <row r="18" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A18" s="2"/>
       <c r="B18" s="13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -1214,7 +1294,7 @@
     <row r="24" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A24" s="2"/>
       <c r="B24" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -1231,28 +1311,28 @@
     <row r="25" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A25" s="2"/>
       <c r="B25" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="H25" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="I25" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -1262,16 +1342,16 @@
     <row r="26" spans="1:13" ht="24" x14ac:dyDescent="0.15">
       <c r="A26" s="2"/>
       <c r="B26" s="9" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F26" s="15">
         <v>5000</v>
@@ -1283,7 +1363,7 @@
         <v>35</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -1293,16 +1373,16 @@
     <row r="27" spans="1:13" ht="24" x14ac:dyDescent="0.15">
       <c r="A27" s="2"/>
       <c r="B27" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C27" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="E27" s="9" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F27" s="15">
         <v>13000</v>
@@ -1314,7 +1394,7 @@
         <v>35</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -1354,7 +1434,7 @@
     <row r="30" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A30" s="2"/>
       <c r="B30" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -1371,19 +1451,19 @@
     <row r="31" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A31" s="2"/>
       <c r="B31" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>0</v>
@@ -1401,19 +1481,19 @@
         <v>1</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D32" s="11">
         <v>250</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F32" s="11">
         <v>1</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -1428,19 +1508,19 @@
         <v>2</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D33" s="11">
         <v>600</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F33" s="11">
         <v>1</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
@@ -1455,19 +1535,19 @@
         <v>3</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D34" s="15">
         <v>1200</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F34" s="11">
         <v>1</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -1482,19 +1562,19 @@
         <v>4</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D35" s="15">
         <v>1600</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F35" s="11">
         <v>1</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -1509,19 +1589,19 @@
         <v>5</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D36" s="15">
         <v>2000</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -1563,7 +1643,7 @@
     <row r="39" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A39" s="16"/>
       <c r="B39" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C39" s="16"/>
       <c r="D39" s="16"/>
@@ -1585,10 +1665,10 @@
       <c r="C40" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="22"/>
       <c r="H40" s="16"/>
       <c r="I40" s="16"/>
       <c r="J40" s="16"/>
@@ -1599,15 +1679,15 @@
     <row r="41" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A41" s="16"/>
       <c r="B41" s="18" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C41" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="21"/>
+        <v>66</v>
+      </c>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="22"/>
       <c r="H41" s="16"/>
       <c r="I41" s="16"/>
       <c r="J41" s="16"/>
@@ -1618,15 +1698,15 @@
     <row r="42" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A42" s="16"/>
       <c r="B42" s="18" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="21"/>
+        <v>68</v>
+      </c>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="22"/>
       <c r="H42" s="16"/>
       <c r="I42" s="16"/>
       <c r="J42" s="16"/>

--- a/domain/tasks/20260310_115400_vd_ingame_masterdata_generation/specs/限界チャレンジ(VD)_アウトゲーム関連_ブロック基礎設計テンプレート.xlsx
+++ b/domain/tasks/20260310_115400_vd_ingame_masterdata_generation/specs/限界チャレンジ(VD)_アウトゲーム関連_ブロック基礎設計テンプレート.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junki.mizutani/Documents/workspace/glow/glow-brain-repos/glow-brain-shuna/domain/tasks/20260310_115400_vd_ingame_masterdata_generation/specs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9091E9-3514-FA4E-86AA-05D4DF12E9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA57F7A-5548-6848-92A7-6BF6DA3B0D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="920" yWindow="660" windowWidth="29320" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="74">
   <si>
     <t>備考</t>
   </si>
@@ -84,9 +84,6 @@
     <t>なし（デフォルトグループのみ）</t>
   </si>
   <si>
-    <t>4〜5行</t>
-  </si>
-  <si>
     <t>※ノーマルブロックは3フロア固定で、ボスブロックは1フロア固定</t>
   </si>
   <si>
@@ -205,9 +202,6 @@
   </si>
   <si>
     <t>条件値（ms）</t>
-  </si>
-  <si>
-    <t>召喚敵</t>
   </si>
   <si>
     <t>体数</t>
@@ -312,6 +306,22 @@
         <charset val="128"/>
       </rPr>
       <t>シーケンス構成</t>
+    </r>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>行</t>
     </r>
     <phoneticPr fontId="13"/>
   </si>
@@ -588,6 +598,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -598,9 +611,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -855,7 +865,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3.1640625" customWidth="1"/>
@@ -911,17 +921,17 @@
     </row>
     <row r="4" spans="1:13" ht="186" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="6"/>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="23"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
@@ -963,7 +973,7 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -992,8 +1002,8 @@
       <c r="F8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="25" t="s">
-        <v>69</v>
+      <c r="G8" s="20" t="s">
+        <v>67</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>12</v>
@@ -1007,22 +1017,22 @@
     <row r="9" spans="1:13" ht="24" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
       <c r="B9" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D9" s="9">
         <v>100</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>13</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="2"/>
@@ -1034,7 +1044,7 @@
     <row r="10" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A10" s="2"/>
       <c r="B10" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -1066,7 +1076,7 @@
     <row r="12" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A12" s="2"/>
       <c r="B12" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -1083,19 +1093,19 @@
     <row r="13" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A13" s="2"/>
       <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -1108,19 +1118,19 @@
     <row r="14" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A14" s="2"/>
       <c r="B14" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="E14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="F14" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>26</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -1133,19 +1143,19 @@
     <row r="15" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A15" s="2"/>
       <c r="B15" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -1158,16 +1168,16 @@
     <row r="16" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A16" s="2"/>
       <c r="B16" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>30</v>
-      </c>
       <c r="D16" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="F16" s="11">
         <v>1</v>
@@ -1198,13 +1208,13 @@
     <row r="18" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A18" s="2"/>
       <c r="B18" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="D18" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -1294,7 +1304,7 @@
     <row r="24" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A24" s="2"/>
       <c r="B24" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -1311,28 +1321,28 @@
     <row r="25" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A25" s="2"/>
       <c r="B25" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="D25" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="E25" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="F25" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="G25" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="H25" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="I25" s="8" t="s">
         <v>41</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>42</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -1342,16 +1352,16 @@
     <row r="26" spans="1:13" ht="24" x14ac:dyDescent="0.15">
       <c r="A26" s="2"/>
       <c r="B26" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="D26" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="E26" s="9" t="s">
         <v>45</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>46</v>
       </c>
       <c r="F26" s="15">
         <v>5000</v>
@@ -1363,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -1373,16 +1383,16 @@
     <row r="27" spans="1:13" ht="24" x14ac:dyDescent="0.15">
       <c r="A27" s="2"/>
       <c r="B27" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="9" t="s">
+      <c r="E27" s="9" t="s">
         <v>49</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>50</v>
       </c>
       <c r="F27" s="15">
         <v>13000</v>
@@ -1394,7 +1404,7 @@
         <v>35</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -1403,14 +1413,14 @@
     </row>
     <row r="28" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="9"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
@@ -1418,14 +1428,14 @@
     </row>
     <row r="29" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="9"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
@@ -1433,16 +1443,14 @@
     </row>
     <row r="30" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A30" s="2"/>
-      <c r="B30" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="9"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
@@ -1450,159 +1458,87 @@
     </row>
     <row r="31" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A31" s="2"/>
-      <c r="B31" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="9"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
     </row>
-    <row r="32" spans="1:13" ht="24" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A32" s="2"/>
-      <c r="B32" s="11">
-        <v>1</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32" s="11">
-        <v>250</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F32" s="11">
-        <v>1</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="9"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
     </row>
-    <row r="33" spans="1:13" ht="24" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A33" s="2"/>
-      <c r="B33" s="11">
-        <v>2</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="11">
-        <v>600</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F33" s="11">
-        <v>1</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="9"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="1:13" ht="24" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A34" s="2"/>
-      <c r="B34" s="11">
-        <v>3</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D34" s="15">
-        <v>1200</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F34" s="11">
-        <v>1</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="9"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
     </row>
-    <row r="35" spans="1:13" ht="24" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A35" s="2"/>
-      <c r="B35" s="11">
-        <v>4</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D35" s="15">
-        <v>1600</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F35" s="11">
-        <v>1</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="9"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
     </row>
-    <row r="36" spans="1:13" ht="24" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A36" s="2"/>
-      <c r="B36" s="11">
-        <v>5</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D36" s="15">
-        <v>2000</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>63</v>
-      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
@@ -1611,190 +1547,531 @@
       <c r="M36" s="2"/>
     </row>
     <row r="37" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A37" s="16"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
     </row>
     <row r="38" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A38" s="16"/>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
+      <c r="A38" s="2"/>
+      <c r="B38" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
     </row>
     <row r="39" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A39" s="16"/>
-      <c r="B39" s="7" t="s">
+      <c r="A39" s="2"/>
+      <c r="B39" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+    </row>
+    <row r="40" spans="1:13" ht="24" x14ac:dyDescent="0.15">
+      <c r="A40" s="2"/>
+      <c r="B40" s="11">
+        <v>1</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" s="11">
+        <v>250</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G40" s="11">
+        <v>1</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" spans="1:13" ht="24" x14ac:dyDescent="0.15">
+      <c r="A41" s="2"/>
+      <c r="B41" s="11">
+        <v>2</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="11">
+        <v>600</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G41" s="11">
+        <v>1</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" spans="1:13" ht="24" x14ac:dyDescent="0.15">
+      <c r="A42" s="2"/>
+      <c r="B42" s="11">
+        <v>3</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D42" s="15">
+        <v>1200</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G42" s="11">
+        <v>1</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" spans="1:13" ht="24" x14ac:dyDescent="0.15">
+      <c r="A43" s="2"/>
+      <c r="B43" s="11">
+        <v>4</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" s="15">
+        <v>1600</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G43" s="11">
+        <v>1</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+    </row>
+    <row r="44" spans="1:13" ht="24" x14ac:dyDescent="0.15">
+      <c r="A44" s="2"/>
+      <c r="B44" s="11">
+        <v>5</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D44" s="15">
+        <v>2000</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+    </row>
+    <row r="45" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A45" s="2"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+    </row>
+    <row r="46" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A46" s="2"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+    </row>
+    <row r="47" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A47" s="2"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+    </row>
+    <row r="48" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A48" s="2"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+    </row>
+    <row r="49" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A49" s="2"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+    </row>
+    <row r="50" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A50" s="2"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+    </row>
+    <row r="51" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A51" s="2"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+    </row>
+    <row r="52" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A52" s="2"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+    </row>
+    <row r="53" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A53" s="2"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+    </row>
+    <row r="54" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A54" s="16"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="16"/>
+      <c r="J54" s="16"/>
+      <c r="K54" s="16"/>
+      <c r="L54" s="16"/>
+      <c r="M54" s="16"/>
+    </row>
+    <row r="55" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A55" s="16"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="16"/>
+      <c r="I55" s="16"/>
+      <c r="J55" s="16"/>
+      <c r="K55" s="16"/>
+      <c r="L55" s="16"/>
+      <c r="M55" s="16"/>
+    </row>
+    <row r="56" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A56" s="16"/>
+      <c r="B56" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" s="16"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="16"/>
+      <c r="H56" s="16"/>
+      <c r="I56" s="16"/>
+      <c r="J56" s="16"/>
+      <c r="K56" s="16"/>
+      <c r="L56" s="16"/>
+      <c r="M56" s="16"/>
+    </row>
+    <row r="57" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A57" s="16"/>
+      <c r="B57" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="23"/>
+      <c r="H57" s="16"/>
+      <c r="I57" s="16"/>
+      <c r="J57" s="16"/>
+      <c r="K57" s="16"/>
+      <c r="L57" s="16"/>
+      <c r="M57" s="16"/>
+    </row>
+    <row r="58" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A58" s="16"/>
+      <c r="B58" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-    </row>
-    <row r="40" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A40" s="16"/>
-      <c r="B40" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-    </row>
-    <row r="41" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A41" s="16"/>
-      <c r="B41" s="18" t="s">
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="23"/>
+      <c r="H58" s="16"/>
+      <c r="I58" s="16"/>
+      <c r="J58" s="16"/>
+      <c r="K58" s="16"/>
+      <c r="L58" s="16"/>
+      <c r="M58" s="16"/>
+    </row>
+    <row r="59" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A59" s="16"/>
+      <c r="B59" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C59" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="16"/>
-      <c r="J41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-    </row>
-    <row r="42" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A42" s="16"/>
-      <c r="B42" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-    </row>
-    <row r="43" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A43" s="16"/>
-      <c r="B43" s="16"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16"/>
-      <c r="I43" s="16"/>
-      <c r="J43" s="16"/>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-    </row>
-    <row r="44" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A44" s="19"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19"/>
-      <c r="K44" s="19"/>
-      <c r="L44" s="19"/>
-      <c r="M44" s="19"/>
-    </row>
-    <row r="45" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A45" s="19"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19"/>
-      <c r="K45" s="19"/>
-      <c r="L45" s="19"/>
-      <c r="M45" s="19"/>
-    </row>
-    <row r="46" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A46" s="19"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19"/>
-      <c r="K46" s="19"/>
-      <c r="L46" s="19"/>
-      <c r="M46" s="19"/>
-    </row>
-    <row r="47" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A47" s="19"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19"/>
-      <c r="K47" s="19"/>
-      <c r="L47" s="19"/>
-      <c r="M47" s="19"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="23"/>
+      <c r="H59" s="16"/>
+      <c r="I59" s="16"/>
+      <c r="J59" s="16"/>
+      <c r="K59" s="16"/>
+      <c r="L59" s="16"/>
+      <c r="M59" s="16"/>
+    </row>
+    <row r="60" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A60" s="16"/>
+      <c r="B60" s="16"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="16"/>
+      <c r="H60" s="16"/>
+      <c r="I60" s="16"/>
+      <c r="J60" s="16"/>
+      <c r="K60" s="16"/>
+      <c r="L60" s="16"/>
+      <c r="M60" s="16"/>
+    </row>
+    <row r="61" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A61" s="19"/>
+      <c r="B61" s="19"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="19"/>
+      <c r="K61" s="19"/>
+      <c r="L61" s="19"/>
+      <c r="M61" s="19"/>
+    </row>
+    <row r="62" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A62" s="19"/>
+      <c r="B62" s="19"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="19"/>
+      <c r="F62" s="19"/>
+      <c r="G62" s="19"/>
+      <c r="H62" s="19"/>
+      <c r="I62" s="19"/>
+      <c r="J62" s="19"/>
+      <c r="K62" s="19"/>
+      <c r="L62" s="19"/>
+      <c r="M62" s="19"/>
+    </row>
+    <row r="63" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A63" s="19"/>
+      <c r="B63" s="19"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="19"/>
+      <c r="F63" s="19"/>
+      <c r="G63" s="19"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="19"/>
+      <c r="K63" s="19"/>
+      <c r="L63" s="19"/>
+      <c r="M63" s="19"/>
+    </row>
+    <row r="64" spans="1:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="A64" s="19"/>
+      <c r="B64" s="19"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="19"/>
+      <c r="M64" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B4:J4"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <conditionalFormatting sqref="E14:F16">
@@ -1803,6 +2080,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
